--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXX/LTAIPT_A63F30.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXX/LTAIPT_A63F30.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="55">
   <si>
     <t>48985</t>
   </si>
@@ -145,7 +145,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Aprobación y reprobación</t>
@@ -157,34 +157,28 @@
     <t>Reporte de índices de reprobación</t>
   </si>
   <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Sub%20Servicios%20Escolares/</t>
+  </si>
+  <si>
     <t>XLS</t>
   </si>
   <si>
     <t>Departamento de Control Escolar</t>
   </si>
   <si>
-    <t>C2AD7FA81589209FA980B78282F9DD37</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20de%20Servicios%20Escolares/PORCENTAJES%20DE%20APROBACI%C3%93N%20POR%20CICLO%202020-2021.pdf</t>
-  </si>
-  <si>
-    <t>https://platrans.tlaxcala.gob.mx/sistemas/trans2016/view_cambios.php?_sess=cetra1534255478022&amp;recno=37421</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20de%20Servicios%20Escolares/PORCENTAJES%20DE%20REPROBACI%C3%93N%20POR%20CICLO%202020-2021.pdf</t>
-  </si>
-  <si>
-    <t>14/07/2022</t>
-  </si>
-  <si>
-    <t>En relación al ciclo escolar que abarca del  21 de febrero de 2022 al 28 de julio de 2022, se informa que debido a que la actividad académica del Colegio de Bachilleres del Estado de Tlaxcala, algunos de  los indicadores se generan por semestre, y la actualización se realiza de manera anual para cubrir el año lectivo autorizado por la Secretaría de Educación Pública.</t>
+    <t>440779A381FDA497DB8F00E1566D3ED1</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>19/07/2023</t>
+  </si>
+  <si>
+    <t>En relación al ciclo escolar que abarca en el periodo del 07 de febrero de 2023 al 21 de julio de 2023 se informa que debido a que la actividad académica del Colegio de Bachilleres del Estado de Tlaxcala, algunos de  los indicadores se generan por semestre, y la actualización se realiza de manera anual para cubrir el año lectivo autorizado por la Secretaría de Educación Pública.</t>
   </si>
 </sst>
 </file>
@@ -580,17 +574,16 @@
   <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="169.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="98.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="87.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="170.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="87.7109375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="20" bestFit="1" customWidth="1"/>
@@ -797,16 +790,16 @@
     </row>
     <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>44</v>
@@ -818,31 +811,31 @@
         <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K8" s="2" t="s">
+      <c r="O8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
